--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/57.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/57.xlsx
@@ -426,13 +426,13 @@
         <v>-18.02239234717236</v>
       </c>
       <c r="E2">
-        <v>-16.67096779195499</v>
+        <v>-16.66709141820442</v>
       </c>
       <c r="F2">
-        <v>3.893261204885348</v>
+        <v>0.7500707970067914</v>
       </c>
       <c r="G2">
-        <v>-12.46137947599578</v>
+        <v>-13.30903056633338</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.16472696208814</v>
       </c>
       <c r="E3">
-        <v>-15.60722924755322</v>
+        <v>-18.08324939530512</v>
       </c>
       <c r="F3">
-        <v>4.067142149672186</v>
+        <v>1.753614711211114</v>
       </c>
       <c r="G3">
-        <v>-12.35191464355115</v>
+        <v>-12.64800223341076</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.22642475602058</v>
       </c>
       <c r="E4">
-        <v>-16.78754429833445</v>
+        <v>-20.07147590837279</v>
       </c>
       <c r="F4">
-        <v>3.713152593964262</v>
+        <v>1.097383711448151</v>
       </c>
       <c r="G4">
-        <v>-11.32229028674831</v>
+        <v>-12.58255170696452</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.29098962989828</v>
       </c>
       <c r="E5">
-        <v>-16.74085120284136</v>
+        <v>-20.00987960492046</v>
       </c>
       <c r="F5">
-        <v>3.223943656892958</v>
+        <v>1.646687390122948</v>
       </c>
       <c r="G5">
-        <v>-10.36422609093541</v>
+        <v>-12.08628663342786</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.37030508160468</v>
       </c>
       <c r="E6">
-        <v>-16.78328753276724</v>
+        <v>-19.79507144036661</v>
       </c>
       <c r="F6">
-        <v>3.468025425597444</v>
+        <v>1.393998884103376</v>
       </c>
       <c r="G6">
-        <v>-9.943232239972414</v>
+        <v>-11.38606082775612</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.4937864843314</v>
       </c>
       <c r="E7">
-        <v>-18.14379056431367</v>
+        <v>-21.73770074865105</v>
       </c>
       <c r="F7">
-        <v>3.652255992714859</v>
+        <v>1.489506332176548</v>
       </c>
       <c r="G7">
-        <v>-10.60156997121628</v>
+        <v>-11.16385978497209</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.6808586093331</v>
       </c>
       <c r="E8">
-        <v>-18.11331393424204</v>
+        <v>-20.70488715324766</v>
       </c>
       <c r="F8">
-        <v>2.659535526995515</v>
+        <v>1.256995199354366</v>
       </c>
       <c r="G8">
-        <v>-9.111255545024289</v>
+        <v>-10.42808522492532</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.95239205700357</v>
       </c>
       <c r="E9">
-        <v>-17.75688227357232</v>
+        <v>-19.99321029209822</v>
       </c>
       <c r="F9">
-        <v>3.18174330792474</v>
+        <v>1.478831989824073</v>
       </c>
       <c r="G9">
-        <v>-9.147463824932762</v>
+        <v>-10.71663256764133</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.30900662833477</v>
       </c>
       <c r="E10">
-        <v>-19.06067522512069</v>
+        <v>-21.21362045174336</v>
       </c>
       <c r="F10">
-        <v>3.315213177333407</v>
+        <v>1.309106135929677</v>
       </c>
       <c r="G10">
-        <v>-8.487862823388507</v>
+        <v>-9.258874421762147</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.75852526027378</v>
       </c>
       <c r="E11">
-        <v>-20.44875666337383</v>
+        <v>-22.56439179264731</v>
       </c>
       <c r="F11">
-        <v>3.206955498196346</v>
+        <v>1.197935917004372</v>
       </c>
       <c r="G11">
-        <v>-8.318358198849152</v>
+        <v>-11.18307133720263</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.30071728141884</v>
       </c>
       <c r="E12">
-        <v>-22.28295619001861</v>
+        <v>-22.59087430864416</v>
       </c>
       <c r="F12">
-        <v>3.179624344108379</v>
+        <v>1.182375863710186</v>
       </c>
       <c r="G12">
-        <v>-6.982320247939131</v>
+        <v>-9.429452005751441</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.929894264060259</v>
       </c>
       <c r="E13">
-        <v>-23.40052470494955</v>
+        <v>-25.37744361842007</v>
       </c>
       <c r="F13">
-        <v>3.377966978299887</v>
+        <v>2.063723988857943</v>
       </c>
       <c r="G13">
-        <v>-6.550629614692347</v>
+        <v>-7.908523782409829</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.656503618649312</v>
       </c>
       <c r="E14">
-        <v>-21.68193259124659</v>
+        <v>-24.39887661315457</v>
       </c>
       <c r="F14">
-        <v>3.588304372483932</v>
+        <v>1.873575565014927</v>
       </c>
       <c r="G14">
-        <v>-6.592927841815149</v>
+        <v>-8.198577205821623</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.475947127346215</v>
       </c>
       <c r="E15">
-        <v>-23.3018401993744</v>
+        <v>-25.29375741875832</v>
       </c>
       <c r="F15">
-        <v>3.565766152188563</v>
+        <v>1.977608570397712</v>
       </c>
       <c r="G15">
-        <v>-6.432170953953273</v>
+        <v>-7.793306968571487</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.384362420908763</v>
       </c>
       <c r="E16">
-        <v>-24.88205120435097</v>
+        <v>-26.48878548159047</v>
       </c>
       <c r="F16">
-        <v>3.822405970719489</v>
+        <v>2.112943923197484</v>
       </c>
       <c r="G16">
-        <v>-5.510246132396092</v>
+        <v>-7.353908745881567</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.37975111284636</v>
       </c>
       <c r="E17">
-        <v>-25.00923339685639</v>
+        <v>-28.35257858587537</v>
       </c>
       <c r="F17">
-        <v>3.54121168563478</v>
+        <v>2.088866596267713</v>
       </c>
       <c r="G17">
-        <v>-5.229790282045673</v>
+        <v>-7.30230497441618</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.454283028998802</v>
       </c>
       <c r="E18">
-        <v>-24.78715250304623</v>
+        <v>-29.253287537527</v>
       </c>
       <c r="F18">
-        <v>4.379000939273727</v>
+        <v>1.94235491046937</v>
       </c>
       <c r="G18">
-        <v>-4.346219659296841</v>
+        <v>-6.69514773705653</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.60151560000511</v>
       </c>
       <c r="E19">
-        <v>-25.5733499324659</v>
+        <v>-29.81050720722282</v>
       </c>
       <c r="F19">
-        <v>4.124367426592381</v>
+        <v>2.092443486713001</v>
       </c>
       <c r="G19">
-        <v>-4.47149669843644</v>
+        <v>-6.102001315755708</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.816312418780351</v>
       </c>
       <c r="E20">
-        <v>-28.07206226347023</v>
+        <v>-29.13528003336112</v>
       </c>
       <c r="F20">
-        <v>4.313894574883297</v>
+        <v>3.029197793964406</v>
       </c>
       <c r="G20">
-        <v>-4.330023549679422</v>
+        <v>-5.913829821764673</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.08035820171281</v>
       </c>
       <c r="E21">
-        <v>-27.9376118701825</v>
+        <v>-30.81315437302411</v>
       </c>
       <c r="F21">
-        <v>4.039297407794484</v>
+        <v>2.510013554055399</v>
       </c>
       <c r="G21">
-        <v>-3.196443531430259</v>
+        <v>-5.381028346163599</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.38647519015845</v>
       </c>
       <c r="E22">
-        <v>-29.72898788237374</v>
+        <v>-31.86999378727519</v>
       </c>
       <c r="F22">
-        <v>4.486786448991193</v>
+        <v>2.886663928434306</v>
       </c>
       <c r="G22">
-        <v>-2.665722350297873</v>
+        <v>-4.9870094176408</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.72446490552667</v>
       </c>
       <c r="E23">
-        <v>-28.84459728680876</v>
+        <v>-32.12224790339846</v>
       </c>
       <c r="F23">
-        <v>3.83676323454481</v>
+        <v>3.846688732765154</v>
       </c>
       <c r="G23">
-        <v>-2.113092452813075</v>
+        <v>-5.388043597857692</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.08107220367767</v>
       </c>
       <c r="E24">
-        <v>-29.66334085892155</v>
+        <v>-31.81790954347597</v>
       </c>
       <c r="F24">
-        <v>4.503940281168365</v>
+        <v>2.941556522748218</v>
       </c>
       <c r="G24">
-        <v>-1.600906892269993</v>
+        <v>-4.780325271611376</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.45042163275673</v>
       </c>
       <c r="E25">
-        <v>-30.51415281971966</v>
+        <v>-32.93564334770819</v>
       </c>
       <c r="F25">
-        <v>4.452594756073241</v>
+        <v>2.903128558932349</v>
       </c>
       <c r="G25">
-        <v>-1.66982238868301</v>
+        <v>-4.885622952675517</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.82091343972283</v>
       </c>
       <c r="E26">
-        <v>-30.21817855128934</v>
+        <v>-33.63319136995371</v>
       </c>
       <c r="F26">
-        <v>4.828837573689971</v>
+        <v>3.541079146850332</v>
       </c>
       <c r="G26">
-        <v>-1.394334307773591</v>
+        <v>-3.617099416572631</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.17822897552633</v>
       </c>
       <c r="E27">
-        <v>-30.98404766088857</v>
+        <v>-32.1890428950116</v>
       </c>
       <c r="F27">
-        <v>4.685632730563603</v>
+        <v>4.053957854089229</v>
       </c>
       <c r="G27">
-        <v>-0.4234766291004105</v>
+        <v>-3.830113038990222</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.51677115564184</v>
       </c>
       <c r="E28">
-        <v>-31.44158882496456</v>
+        <v>-30.73674769532969</v>
       </c>
       <c r="F28">
-        <v>5.150562219058854</v>
+        <v>3.581541581007477</v>
       </c>
       <c r="G28">
-        <v>-0.07590667297311006</v>
+        <v>-4.627745187875638</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.82750688125131</v>
       </c>
       <c r="E29">
-        <v>-30.13472783227599</v>
+        <v>-34.24894156619867</v>
       </c>
       <c r="F29">
-        <v>4.568819672890428</v>
+        <v>3.637489515392555</v>
       </c>
       <c r="G29">
-        <v>-1.161751479975472</v>
+        <v>-4.300298963572412</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.10137571971525</v>
       </c>
       <c r="E30">
-        <v>-29.83819429730572</v>
+        <v>-32.02596801752138</v>
       </c>
       <c r="F30">
-        <v>4.627670206654916</v>
+        <v>3.663228547332341</v>
       </c>
       <c r="G30">
-        <v>-0.07607073405108229</v>
+        <v>-3.751281691024563</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.33648101044228</v>
       </c>
       <c r="E31">
-        <v>-30.25879896313814</v>
+        <v>-31.06190797873945</v>
       </c>
       <c r="F31">
-        <v>4.718391347874713</v>
+        <v>3.295294254765691</v>
       </c>
       <c r="G31">
-        <v>-0.9248407209404441</v>
+        <v>-4.135496329527742</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.52172470718209</v>
       </c>
       <c r="E32">
-        <v>-29.8904913793833</v>
+        <v>-31.40590897825812</v>
       </c>
       <c r="F32">
-        <v>4.184415779621317</v>
+        <v>3.547638159945699</v>
       </c>
       <c r="G32">
-        <v>-0.8646992109773819</v>
+        <v>-2.642058180411158</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.65331190531875</v>
       </c>
       <c r="E33">
-        <v>-30.75362305371928</v>
+        <v>-31.07364125489332</v>
       </c>
       <c r="F33">
-        <v>4.561833222215217</v>
+        <v>2.965764731727631</v>
       </c>
       <c r="G33">
-        <v>-1.861114324377078</v>
+        <v>-2.522162344629048</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.72993128738823</v>
       </c>
       <c r="E34">
-        <v>-29.32592878908404</v>
+        <v>-30.10856004522266</v>
       </c>
       <c r="F34">
-        <v>4.818333875022473</v>
+        <v>3.393411060157681</v>
       </c>
       <c r="G34">
-        <v>-1.50649630434009</v>
+        <v>-3.676561713672888</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.74776387411301</v>
       </c>
       <c r="E35">
-        <v>-29.48694321090077</v>
+        <v>-30.75254301266845</v>
       </c>
       <c r="F35">
-        <v>4.382667293398518</v>
+        <v>2.979434450608628</v>
       </c>
       <c r="G35">
-        <v>-0.8506982385832313</v>
+        <v>-3.129595204599692</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.71000400754224</v>
       </c>
       <c r="E36">
-        <v>-29.36231507773567</v>
+        <v>-30.32014620052005</v>
       </c>
       <c r="F36">
-        <v>4.760803758898048</v>
+        <v>3.411873712831276</v>
       </c>
       <c r="G36">
-        <v>-1.035926476835445</v>
+        <v>-3.49732826720978</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.62094378898562</v>
       </c>
       <c r="E37">
-        <v>-29.30174673788308</v>
+        <v>-29.89509457321209</v>
       </c>
       <c r="F37">
-        <v>4.41006803034832</v>
+        <v>2.879708955720401</v>
       </c>
       <c r="G37">
-        <v>-2.57828763940335</v>
+        <v>-3.520241037359382</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.47926092384133</v>
       </c>
       <c r="E38">
-        <v>-27.01411110885027</v>
+        <v>-29.33215091237058</v>
       </c>
       <c r="F38">
-        <v>4.772992356862839</v>
+        <v>3.028675922500642</v>
       </c>
       <c r="G38">
-        <v>-1.600828142952566</v>
+        <v>-4.764342441395321</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.29538436771901</v>
       </c>
       <c r="E39">
-        <v>-29.45893912763733</v>
+        <v>-28.65597275896726</v>
       </c>
       <c r="F39">
-        <v>5.332486611326876</v>
+        <v>3.31762538321036</v>
       </c>
       <c r="G39">
-        <v>-1.844265251669329</v>
+        <v>-4.806463482553913</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.07743994835375</v>
       </c>
       <c r="E40">
-        <v>-27.22134313638928</v>
+        <v>-29.01443770446643</v>
       </c>
       <c r="F40">
-        <v>5.060228753783568</v>
+        <v>3.956352979752169</v>
       </c>
       <c r="G40">
-        <v>-2.668596700383947</v>
+        <v>-5.664401202480364</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.82972062017511</v>
       </c>
       <c r="E41">
-        <v>-27.44346478646551</v>
+        <v>-27.70029718981053</v>
       </c>
       <c r="F41">
-        <v>5.013520429409315</v>
+        <v>3.753999390596306</v>
       </c>
       <c r="G41">
-        <v>-2.992479518073615</v>
+        <v>-4.491141371912835</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.56842232353946</v>
       </c>
       <c r="E42">
-        <v>-26.11652227578993</v>
+        <v>-26.23218855889384</v>
       </c>
       <c r="F42">
-        <v>4.990177035998425</v>
+        <v>3.684414872026342</v>
       </c>
       <c r="G42">
-        <v>-2.259201967633589</v>
+        <v>-4.799654947818065</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.29905828506263</v>
       </c>
       <c r="E43">
-        <v>-25.28773907680213</v>
+        <v>-23.57584457615651</v>
       </c>
       <c r="F43">
-        <v>5.170703144090521</v>
+        <v>3.853560868738779</v>
       </c>
       <c r="G43">
-        <v>-1.821910289184832</v>
+        <v>-5.149610352019082</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.02679040501597</v>
       </c>
       <c r="E44">
-        <v>-25.5938956190387</v>
+        <v>-25.7071346400745</v>
       </c>
       <c r="F44">
-        <v>5.213561216776561</v>
+        <v>2.994169449969626</v>
       </c>
       <c r="G44">
-        <v>-2.857955996579501</v>
+        <v>-4.765789460103036</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.75938698944904</v>
       </c>
       <c r="E45">
-        <v>-24.90515547873811</v>
+        <v>-26.6149714098142</v>
       </c>
       <c r="F45">
-        <v>5.418663328974914</v>
+        <v>3.567895056413758</v>
       </c>
       <c r="G45">
-        <v>-3.206375789090698</v>
+        <v>-6.270761103001069</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.49927833285085</v>
       </c>
       <c r="E46">
-        <v>-23.06767733691177</v>
+        <v>-24.56252660684376</v>
       </c>
       <c r="F46">
-        <v>5.850703318109413</v>
+        <v>3.603296165739797</v>
       </c>
       <c r="G46">
-        <v>-3.3104791055072</v>
+        <v>-4.296558370994645</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.24959432162746</v>
       </c>
       <c r="E47">
-        <v>-23.43424372241067</v>
+        <v>-24.66831175966294</v>
       </c>
       <c r="F47">
-        <v>5.812820420044586</v>
+        <v>3.564796962327287</v>
       </c>
       <c r="G47">
-        <v>-4.066285523174375</v>
+        <v>-5.233370094767028</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.01689944322254</v>
       </c>
       <c r="E48">
-        <v>-23.2263912939326</v>
+        <v>-25.73787845011258</v>
       </c>
       <c r="F48">
-        <v>5.864073167990597</v>
+        <v>3.907863665461897</v>
       </c>
       <c r="G48">
-        <v>-4.079810718442405</v>
+        <v>-5.89080220886049</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.7963101858241</v>
       </c>
       <c r="E49">
-        <v>-22.19883525685212</v>
+        <v>-23.17050086772994</v>
       </c>
       <c r="F49">
-        <v>5.651542256923939</v>
+        <v>4.465656453280584</v>
       </c>
       <c r="G49">
-        <v>-5.120843882607431</v>
+        <v>-6.352033679806955</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.58949268829454</v>
       </c>
       <c r="E50">
-        <v>-21.27149887803539</v>
+        <v>-22.65310006998356</v>
       </c>
       <c r="F50">
-        <v>6.219416276034695</v>
+        <v>4.137947681793877</v>
       </c>
       <c r="G50">
-        <v>-4.376167368469893</v>
+        <v>-5.842266379553183</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.39627102620296</v>
       </c>
       <c r="E51">
-        <v>-21.11335550873953</v>
+        <v>-20.84709029403653</v>
       </c>
       <c r="F51">
-        <v>5.77950348310399</v>
+        <v>3.733773972089553</v>
       </c>
       <c r="G51">
-        <v>-2.644919405610993</v>
+        <v>-4.670374818375944</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.21214240449999</v>
       </c>
       <c r="E52">
-        <v>-20.02689761024128</v>
+        <v>-23.49253876831141</v>
       </c>
       <c r="F52">
-        <v>5.94481579547627</v>
+        <v>4.082982191148519</v>
       </c>
       <c r="G52">
-        <v>-5.037359762470478</v>
+        <v>-5.676810782418183</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.04098415744864</v>
       </c>
       <c r="E53">
-        <v>-21.00710392309756</v>
+        <v>-19.57611519362175</v>
       </c>
       <c r="F53">
-        <v>6.111587691212284</v>
+        <v>4.473686646883322</v>
       </c>
       <c r="G53">
-        <v>-4.550337890066777</v>
+        <v>-6.20729243437673</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.882301378535992</v>
       </c>
       <c r="E54">
-        <v>-18.60609794728272</v>
+        <v>-20.53146471264992</v>
       </c>
       <c r="F54">
-        <v>5.976987928666198</v>
+        <v>3.721351774517172</v>
       </c>
       <c r="G54">
-        <v>-4.775268909188273</v>
+        <v>-6.598971851927645</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.731920062449435</v>
       </c>
       <c r="E55">
-        <v>-17.76025145823402</v>
+        <v>-17.87657889854306</v>
       </c>
       <c r="F55">
-        <v>6.539224079233501</v>
+        <v>3.752052727199727</v>
       </c>
       <c r="G55">
-        <v>-4.387979766083894</v>
+        <v>-6.751784902394105</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.592246069596078</v>
       </c>
       <c r="E56">
-        <v>-16.69750917811394</v>
+        <v>-19.10152206066988</v>
       </c>
       <c r="F56">
-        <v>6.06229320380649</v>
+        <v>4.477036564660243</v>
       </c>
       <c r="G56">
-        <v>-5.396318838630612</v>
+        <v>-6.297827899644928</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.463335257937656</v>
       </c>
       <c r="E57">
-        <v>-18.54487750717303</v>
+        <v>-18.17140519881244</v>
       </c>
       <c r="F57">
-        <v>6.589171320152699</v>
+        <v>3.907714559329393</v>
       </c>
       <c r="G57">
-        <v>-4.999389466584584</v>
+        <v>-6.995835599542484</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.343730478656243</v>
       </c>
       <c r="E58">
-        <v>-16.62538417259378</v>
+        <v>-17.6544980047329</v>
       </c>
       <c r="F58">
-        <v>6.213168729082781</v>
+        <v>3.806502973320544</v>
       </c>
       <c r="G58">
-        <v>-4.841388804832643</v>
+        <v>-7.669572103564827</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.240712447940707</v>
       </c>
       <c r="E59">
-        <v>-16.11312772132012</v>
+        <v>-17.89634115911253</v>
       </c>
       <c r="F59">
-        <v>5.971118117249961</v>
+        <v>3.855325291306742</v>
       </c>
       <c r="G59">
-        <v>-5.563989260318237</v>
+        <v>-7.365625988070344</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.151861213358613</v>
       </c>
       <c r="E60">
-        <v>-16.03730295253568</v>
+        <v>-19.64757451346278</v>
       </c>
       <c r="F60">
-        <v>6.035293396679643</v>
+        <v>4.628616202228914</v>
       </c>
       <c r="G60">
-        <v>-4.606312248649346</v>
+        <v>-7.570646554769128</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.077172681531442</v>
       </c>
       <c r="E61">
-        <v>-15.03823554543746</v>
+        <v>-17.59470856240963</v>
       </c>
       <c r="F61">
-        <v>6.242527726572801</v>
+        <v>3.554773716753413</v>
       </c>
       <c r="G61">
-        <v>-5.23814099091446</v>
+        <v>-7.33285642835617</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.017691933940448</v>
       </c>
       <c r="E62">
-        <v>-15.31638347593658</v>
+        <v>-16.61617778493618</v>
       </c>
       <c r="F62">
-        <v>6.215223080241724</v>
+        <v>4.252043694385869</v>
       </c>
       <c r="G62">
-        <v>-4.884005310446711</v>
+        <v>-7.824567166368317</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.97066112407089</v>
       </c>
       <c r="E63">
-        <v>-14.68852866866912</v>
+        <v>-15.70183359804746</v>
       </c>
       <c r="F63">
-        <v>5.984890553688905</v>
+        <v>3.90613072085524</v>
       </c>
       <c r="G63">
-        <v>-5.770509345269687</v>
+        <v>-8.614265321522996</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.937096277120085</v>
       </c>
       <c r="E64">
-        <v>-15.16927599779741</v>
+        <v>-15.32572571781441</v>
       </c>
       <c r="F64">
-        <v>5.650226809488293</v>
+        <v>3.942542438412695</v>
       </c>
       <c r="G64">
-        <v>-5.982607506872194</v>
+        <v>-8.962094494153492</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.91835193318869</v>
       </c>
       <c r="E65">
-        <v>-14.22390723548214</v>
+        <v>-15.46610388357818</v>
       </c>
       <c r="F65">
-        <v>5.768514361138451</v>
+        <v>3.708304987923079</v>
       </c>
       <c r="G65">
-        <v>-5.198008370020892</v>
+        <v>-8.92322842478187</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.907875026141133</v>
       </c>
       <c r="E66">
-        <v>-15.6202621957473</v>
+        <v>-14.90988953511206</v>
       </c>
       <c r="F66">
-        <v>5.73992740206784</v>
+        <v>3.639608479208917</v>
       </c>
       <c r="G66">
-        <v>-5.725907700612155</v>
+        <v>-7.564576294884155</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.907708703096528</v>
       </c>
       <c r="E67">
-        <v>-13.91108025103227</v>
+        <v>-14.09087425455881</v>
       </c>
       <c r="F67">
-        <v>5.299946683010106</v>
+        <v>3.352022511244206</v>
       </c>
       <c r="G67">
-        <v>-6.262039616096065</v>
+        <v>-7.7207886908862</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.917317443904821</v>
       </c>
       <c r="E68">
-        <v>-14.7846319440599</v>
+        <v>-16.09413982980595</v>
       </c>
       <c r="F68">
-        <v>5.42457124529168</v>
+        <v>4.016850307913423</v>
       </c>
       <c r="G68">
-        <v>-5.737516662489471</v>
+        <v>-8.060135905785531</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.933607982780641</v>
       </c>
       <c r="E69">
-        <v>-15.36143273536489</v>
+        <v>-15.56554917278662</v>
       </c>
       <c r="F69">
-        <v>5.369544455458515</v>
+        <v>3.307496106608927</v>
       </c>
       <c r="G69">
-        <v>-4.650648114360562</v>
+        <v>-7.61341727779649</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.961703359593088</v>
       </c>
       <c r="E70">
-        <v>-13.74166098145731</v>
+        <v>-15.37332450810903</v>
       </c>
       <c r="F70">
-        <v>5.250431849875168</v>
+        <v>3.162197150688283</v>
       </c>
       <c r="G70">
-        <v>-4.872708064617543</v>
+        <v>-7.0577850625848</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.000142433078235</v>
       </c>
       <c r="E71">
-        <v>-12.90470841535967</v>
+        <v>-14.25218755566004</v>
       </c>
       <c r="F71">
-        <v>5.043195863247204</v>
+        <v>3.114849326679069</v>
       </c>
       <c r="G71">
-        <v>-4.72754026038459</v>
+        <v>-8.334747900538579</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.047010242319649</v>
       </c>
       <c r="E72">
-        <v>-14.57096042648198</v>
+        <v>-16.18903400263669</v>
       </c>
       <c r="F72">
-        <v>5.074513121277443</v>
+        <v>2.851802914654892</v>
       </c>
       <c r="G72">
-        <v>-4.930641312471098</v>
+        <v>-7.248089350589475</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.105132015421516</v>
       </c>
       <c r="E73">
-        <v>-13.43545462600665</v>
+        <v>-16.72405962122091</v>
       </c>
       <c r="F73">
-        <v>4.247076803438683</v>
+        <v>2.88180638198429</v>
       </c>
       <c r="G73">
-        <v>-5.343789762685462</v>
+        <v>-8.213877541953314</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.174176984976649</v>
       </c>
       <c r="E74">
-        <v>-13.84648609778686</v>
+        <v>-15.17418939209574</v>
       </c>
       <c r="F74">
-        <v>4.555431598926383</v>
+        <v>2.75195482139105</v>
       </c>
       <c r="G74">
-        <v>-3.75171153104885</v>
+        <v>-7.388768443729107</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.254558321685453</v>
       </c>
       <c r="E75">
-        <v>-13.38711769444878</v>
+        <v>-13.00299894369616</v>
       </c>
       <c r="F75">
-        <v>4.457089477600831</v>
+        <v>3.710965704020872</v>
       </c>
       <c r="G75">
-        <v>-5.206555952183245</v>
+        <v>-7.56886157024079</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.350338917985288</v>
       </c>
       <c r="E76">
-        <v>-13.29831431915837</v>
+        <v>-15.33434793232501</v>
       </c>
       <c r="F76">
-        <v>4.542475932746599</v>
+        <v>2.330710116249834</v>
       </c>
       <c r="G76">
-        <v>-5.253251016195703</v>
+        <v>-6.384288087736296</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.456059409209056</v>
       </c>
       <c r="E77">
-        <v>-13.22563231133526</v>
+        <v>-15.15052358693165</v>
       </c>
       <c r="F77">
-        <v>4.194210395792019</v>
+        <v>2.941793435825419</v>
       </c>
       <c r="G77">
-        <v>-4.969874878657379</v>
+        <v>-6.136171957075765</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.573251779122934</v>
       </c>
       <c r="E78">
-        <v>-14.00221579043664</v>
+        <v>-14.47105323292476</v>
       </c>
       <c r="F78">
-        <v>4.087674064117975</v>
+        <v>2.533522620946849</v>
       </c>
       <c r="G78">
-        <v>-4.90008329608799</v>
+        <v>-5.472840206618422</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.702617723037527</v>
       </c>
       <c r="E79">
-        <v>-15.23514265223898</v>
+        <v>-16.7196217166934</v>
       </c>
       <c r="F79">
-        <v>3.684688233269266</v>
+        <v>2.483038597950635</v>
       </c>
       <c r="G79">
-        <v>-3.538369786475314</v>
+        <v>-7.819825801214919</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.842006135001078</v>
       </c>
       <c r="E80">
-        <v>-15.52884589095445</v>
+        <v>-15.74700512627397</v>
       </c>
       <c r="F80">
-        <v>3.467102624310725</v>
+        <v>2.377146736115969</v>
       </c>
       <c r="G80">
-        <v>-2.289904357765313</v>
+        <v>-5.776028359932673</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.99440119893716</v>
       </c>
       <c r="E81">
-        <v>-16.37169453021008</v>
+        <v>-16.14850416026804</v>
       </c>
       <c r="F81">
-        <v>4.095652898941739</v>
+        <v>2.342961670137239</v>
       </c>
       <c r="G81">
-        <v>-3.748614057896734</v>
+        <v>-7.151552531089052</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.15943097654377</v>
       </c>
       <c r="E82">
-        <v>-17.63440516556086</v>
+        <v>-17.54826000451295</v>
       </c>
       <c r="F82">
-        <v>3.713442522555242</v>
+        <v>2.280617082667743</v>
       </c>
       <c r="G82">
-        <v>-2.77612561210851</v>
+        <v>-6.358550185824012</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.33072546284817</v>
       </c>
       <c r="E83">
-        <v>-17.53250997191427</v>
+        <v>-17.57145031990623</v>
       </c>
       <c r="F83">
-        <v>4.239634750691933</v>
+        <v>2.044330251223601</v>
       </c>
       <c r="G83">
-        <v>-2.421855401556823</v>
+        <v>-5.134375640318581</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.51038650605064</v>
       </c>
       <c r="E84">
-        <v>-18.58904824264384</v>
+        <v>-18.21051310034268</v>
       </c>
       <c r="F84">
-        <v>3.700867905380746</v>
+        <v>2.141915244742993</v>
       </c>
       <c r="G84">
-        <v>-3.075317237563357</v>
+        <v>-7.344567108101828</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.69655488546024</v>
       </c>
       <c r="E85">
-        <v>-18.97922156314472</v>
+        <v>-20.77354787615196</v>
       </c>
       <c r="F85">
-        <v>3.817217077308353</v>
+        <v>2.175614887423683</v>
       </c>
       <c r="G85">
-        <v>-2.805650043700393</v>
+        <v>-4.371793500131153</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.88485593721687</v>
       </c>
       <c r="E86">
-        <v>-20.80075494799005</v>
+        <v>-20.26036761618073</v>
       </c>
       <c r="F86">
-        <v>3.541934022010021</v>
+        <v>1.541705075696556</v>
       </c>
       <c r="G86">
-        <v>-2.087718766493889</v>
+        <v>-5.783158454381346</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.07910577042549</v>
       </c>
       <c r="E87">
-        <v>-19.96550055964529</v>
+        <v>-23.01705805445403</v>
       </c>
       <c r="F87">
-        <v>3.839735416786055</v>
+        <v>1.869165336962423</v>
       </c>
       <c r="G87">
-        <v>-2.326339041961387</v>
+        <v>-3.876105921588959</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.27304414034593</v>
       </c>
       <c r="E88">
-        <v>-22.39918853237348</v>
+        <v>-23.86456649346355</v>
       </c>
       <c r="F88">
-        <v>3.165707771741347</v>
+        <v>2.64056094326699</v>
       </c>
       <c r="G88">
-        <v>-2.393407210636437</v>
+        <v>-4.792505166040035</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.46482968067133</v>
       </c>
       <c r="E89">
-        <v>-22.67251363805444</v>
+        <v>-23.68062893622</v>
       </c>
       <c r="F89">
-        <v>3.854793479434144</v>
+        <v>1.689540492604572</v>
       </c>
       <c r="G89">
-        <v>-1.6503811509433</v>
+        <v>-4.65338137191958</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.65520445495878</v>
       </c>
       <c r="E90">
-        <v>-26.11928917340861</v>
+        <v>-27.70026549049248</v>
       </c>
       <c r="F90">
-        <v>3.092632512935986</v>
+        <v>1.227018239781857</v>
       </c>
       <c r="G90">
-        <v>-1.686628805510486</v>
+        <v>-3.773256031808164</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.84114855211327</v>
       </c>
       <c r="E91">
-        <v>-26.78268797316228</v>
+        <v>-27.28757659722547</v>
       </c>
       <c r="F91">
-        <v>2.964217341419201</v>
+        <v>1.467438624565969</v>
       </c>
       <c r="G91">
-        <v>-2.695473186177358</v>
+        <v>-3.212646203490797</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.02382392673823</v>
       </c>
       <c r="E92">
-        <v>-29.1917682181328</v>
+        <v>-28.7923160543902</v>
       </c>
       <c r="F92">
-        <v>3.093088115007526</v>
+        <v>1.405610938355819</v>
       </c>
       <c r="G92">
-        <v>-1.159425093889825</v>
+        <v>-3.340774624165553</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.2061311877234</v>
       </c>
       <c r="E93">
-        <v>-28.61765281191436</v>
+        <v>-28.98416485572516</v>
       </c>
       <c r="F93">
-        <v>2.889352809023793</v>
+        <v>0.7072491724864738</v>
       </c>
       <c r="G93">
-        <v>-0.9487411387794394</v>
+        <v>-4.111067635017676</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.38058118056231</v>
       </c>
       <c r="E94">
-        <v>-32.29024523213501</v>
+        <v>-33.18539321770523</v>
       </c>
       <c r="F94">
-        <v>2.999162848673701</v>
+        <v>1.131106548416119</v>
       </c>
       <c r="G94">
-        <v>-1.964019994924383</v>
+        <v>-4.648823755173511</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.55281188875519</v>
       </c>
       <c r="E95">
-        <v>-33.05607358546818</v>
+        <v>-34.87926892027432</v>
       </c>
       <c r="F95">
-        <v>2.486509457368365</v>
+        <v>0.5741371577958156</v>
       </c>
       <c r="G95">
-        <v>-1.511916882356293</v>
+        <v>-3.322704937037691</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.72513334687878</v>
       </c>
       <c r="E96">
-        <v>-35.99848127127005</v>
+        <v>-36.81396887057133</v>
       </c>
       <c r="F96">
-        <v>2.110369357309583</v>
+        <v>0.2313065393710038</v>
       </c>
       <c r="G96">
-        <v>-0.8493135630851457</v>
+        <v>-5.313914240386717</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.8935728169717</v>
       </c>
       <c r="E97">
-        <v>-38.51374970324643</v>
+        <v>-37.61621747611118</v>
       </c>
       <c r="F97">
-        <v>1.918309061500906</v>
+        <v>0.2153265038035985</v>
       </c>
       <c r="G97">
-        <v>-1.03565741666757</v>
+        <v>-4.79833261552961</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-13.06654854048854</v>
       </c>
       <c r="E98">
-        <v>-39.52046343870661</v>
+        <v>-42.09140040165927</v>
       </c>
       <c r="F98">
-        <v>1.515157557171637</v>
+        <v>-0.3842640464255452</v>
       </c>
       <c r="G98">
-        <v>-2.248580653445666</v>
+        <v>-5.344468975548266</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.23697800812318</v>
       </c>
       <c r="E99">
-        <v>-41.67198446025387</v>
+        <v>-43.36134980271132</v>
       </c>
       <c r="F99">
-        <v>0.9917569271823807</v>
+        <v>-0.1374867701923501</v>
       </c>
       <c r="G99">
-        <v>-0.8506326141520425</v>
+        <v>-3.060617364977045</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.4066167702217</v>
       </c>
       <c r="E100">
-        <v>-45.45742192427166</v>
+        <v>-45.00846221844021</v>
       </c>
       <c r="F100">
-        <v>1.252079667186153</v>
+        <v>-0.2555075875388069</v>
       </c>
       <c r="G100">
-        <v>-1.737907736041488</v>
+        <v>-5.109901008706682</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.56496882574529</v>
       </c>
       <c r="E101">
-        <v>-46.91492034058838</v>
+        <v>-47.64334123438119</v>
       </c>
       <c r="F101">
-        <v>1.2023825932226</v>
+        <v>-0.0003132701257659653</v>
       </c>
       <c r="G101">
-        <v>-1.342884753721498</v>
+        <v>-6.879647544122546</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.72676017508695</v>
       </c>
       <c r="E102">
-        <v>-49.26402434368281</v>
+        <v>-49.44896269368206</v>
       </c>
       <c r="F102">
-        <v>0.7578640775323291</v>
+        <v>-0.9027623981250341</v>
       </c>
       <c r="G102">
-        <v>-2.123457831719361</v>
+        <v>-5.587062810324252</v>
       </c>
     </row>
   </sheetData>
